--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129085301</v>
+        <v>129085277</v>
       </c>
       <c r="B11" t="n">
-        <v>92811</v>
+        <v>90555</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768280</v>
+        <v>768461</v>
       </c>
       <c r="R11" t="n">
-        <v>7289244</v>
+        <v>7289280</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,32 +1718,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085280</v>
+        <v>129085301</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>92816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768287</v>
+        <v>768280</v>
       </c>
       <c r="R12" t="n">
-        <v>7289247</v>
+        <v>7289244</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1789,11 +1789,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129085277</v>
+        <v>129085280</v>
       </c>
       <c r="B13" t="n">
-        <v>90552</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1831,21 +1826,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768461</v>
+        <v>768287</v>
       </c>
       <c r="R13" t="n">
-        <v>7289280</v>
+        <v>7289247</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1891,6 +1886,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2017,7 @@
         <v>129085278</v>
       </c>
       <c r="B15" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>129085303</v>
       </c>
       <c r="B16" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>129085286</v>
       </c>
       <c r="B17" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>129085288</v>
       </c>
       <c r="B19" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129085302</v>
       </c>
       <c r="B20" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129085299</v>
       </c>
       <c r="B21" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129085298</v>
       </c>
       <c r="B24" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129085300</v>
       </c>
       <c r="B25" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129085289</v>
       </c>
       <c r="B26" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>129085295</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3377,32 +3377,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129085281</v>
+        <v>129085290</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>79058</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768299</v>
+        <v>768447</v>
       </c>
       <c r="R29" t="n">
-        <v>7289244</v>
+        <v>7289274</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3448,11 +3448,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3479,32 +3474,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129085290</v>
+        <v>129085281</v>
       </c>
       <c r="B30" t="n">
-        <v>79058</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3514,10 +3509,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768447</v>
+        <v>768299</v>
       </c>
       <c r="R30" t="n">
-        <v>7289274</v>
+        <v>7289244</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3550,6 +3545,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>129085292</v>
       </c>
       <c r="B10" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>129085277</v>
       </c>
       <c r="B11" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,32 +1718,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085301</v>
+        <v>129085280</v>
       </c>
       <c r="B12" t="n">
-        <v>92816</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768280</v>
+        <v>768287</v>
       </c>
       <c r="R12" t="n">
-        <v>7289244</v>
+        <v>7289247</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1789,6 +1789,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,32 +1820,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129085280</v>
+        <v>129085301</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768287</v>
+        <v>768280</v>
       </c>
       <c r="R13" t="n">
-        <v>7289247</v>
+        <v>7289244</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1886,11 +1891,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,7 +1920,7 @@
         <v>129085297</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>129085278</v>
       </c>
       <c r="B15" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,32 +2111,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129085303</v>
+        <v>129085286</v>
       </c>
       <c r="B16" t="n">
-        <v>92816</v>
+        <v>92850</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768495</v>
+        <v>768470</v>
       </c>
       <c r="R16" t="n">
-        <v>7289476</v>
+        <v>7289279</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2208,32 +2208,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129085286</v>
+        <v>129085303</v>
       </c>
       <c r="B17" t="n">
-        <v>92847</v>
+        <v>92819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768470</v>
+        <v>768495</v>
       </c>
       <c r="R17" t="n">
-        <v>7289279</v>
+        <v>7289476</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,7 +2405,7 @@
         <v>129085288</v>
       </c>
       <c r="B19" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129085302</v>
       </c>
       <c r="B20" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129085299</v>
       </c>
       <c r="B21" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>129085293</v>
       </c>
       <c r="B23" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129085298</v>
       </c>
       <c r="B24" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129085300</v>
       </c>
       <c r="B25" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129085289</v>
       </c>
       <c r="B26" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>129085291</v>
       </c>
       <c r="B27" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>129085295</v>
       </c>
       <c r="B28" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>129085290</v>
       </c>
       <c r="B29" t="n">
-        <v>79058</v>
+        <v>79059</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1718,32 +1718,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085280</v>
+        <v>129085301</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768287</v>
+        <v>768280</v>
       </c>
       <c r="R12" t="n">
-        <v>7289247</v>
+        <v>7289244</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1789,11 +1789,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,32 +1815,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129085301</v>
+        <v>129085280</v>
       </c>
       <c r="B13" t="n">
-        <v>92819</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768280</v>
+        <v>768287</v>
       </c>
       <c r="R13" t="n">
-        <v>7289244</v>
+        <v>7289247</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1891,6 +1886,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129085297</v>
+        <v>129085278</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>90558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768241</v>
+        <v>768498</v>
       </c>
       <c r="R14" t="n">
-        <v>7289178</v>
+        <v>7289313</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129085278</v>
+        <v>129085297</v>
       </c>
       <c r="B15" t="n">
-        <v>90558</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768498</v>
+        <v>768241</v>
       </c>
       <c r="R15" t="n">
-        <v>7289313</v>
+        <v>7289178</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129085278</v>
+        <v>129085297</v>
       </c>
       <c r="B14" t="n">
-        <v>90558</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768498</v>
+        <v>768241</v>
       </c>
       <c r="R14" t="n">
-        <v>7289313</v>
+        <v>7289178</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129085297</v>
+        <v>129085278</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>90558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768241</v>
+        <v>768498</v>
       </c>
       <c r="R15" t="n">
-        <v>7289178</v>
+        <v>7289313</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2111,32 +2111,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129085286</v>
+        <v>129085303</v>
       </c>
       <c r="B16" t="n">
-        <v>92850</v>
+        <v>92819</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768470</v>
+        <v>768495</v>
       </c>
       <c r="R16" t="n">
-        <v>7289279</v>
+        <v>7289476</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2208,32 +2208,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129085303</v>
+        <v>129085286</v>
       </c>
       <c r="B17" t="n">
-        <v>92819</v>
+        <v>92850</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768495</v>
+        <v>768470</v>
       </c>
       <c r="R17" t="n">
-        <v>7289476</v>
+        <v>7289279</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129085297</v>
+        <v>129085278</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>90558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768241</v>
+        <v>768498</v>
       </c>
       <c r="R14" t="n">
-        <v>7289178</v>
+        <v>7289313</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129085278</v>
+        <v>129085297</v>
       </c>
       <c r="B15" t="n">
-        <v>90558</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768498</v>
+        <v>768241</v>
       </c>
       <c r="R15" t="n">
-        <v>7289313</v>
+        <v>7289178</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>129085282</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>129085292</v>
       </c>
       <c r="B10" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129085277</v>
+        <v>129085301</v>
       </c>
       <c r="B11" t="n">
-        <v>90558</v>
+        <v>92826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768461</v>
+        <v>768280</v>
       </c>
       <c r="R11" t="n">
-        <v>7289280</v>
+        <v>7289244</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,32 +1718,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085301</v>
+        <v>129085277</v>
       </c>
       <c r="B12" t="n">
-        <v>92819</v>
+        <v>90562</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768280</v>
+        <v>768461</v>
       </c>
       <c r="R12" t="n">
-        <v>7289244</v>
+        <v>7289280</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1818,7 +1818,7 @@
         <v>129085280</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>129085278</v>
       </c>
       <c r="B14" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>129085297</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>129085303</v>
       </c>
       <c r="B16" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>129085286</v>
       </c>
       <c r="B17" t="n">
-        <v>92850</v>
+        <v>92857</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>129085294</v>
       </c>
       <c r="B18" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>129085288</v>
       </c>
       <c r="B19" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129085302</v>
       </c>
       <c r="B20" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129085299</v>
       </c>
       <c r="B21" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>129085296</v>
       </c>
       <c r="B22" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>129085293</v>
       </c>
       <c r="B23" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129085298</v>
       </c>
       <c r="B24" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129085300</v>
       </c>
       <c r="B25" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129085289</v>
       </c>
       <c r="B26" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3178,32 +3178,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129085291</v>
+        <v>129085295</v>
       </c>
       <c r="B27" t="n">
-        <v>78793</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768164</v>
+        <v>768282</v>
       </c>
       <c r="R27" t="n">
-        <v>7289156</v>
+        <v>7289198</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3249,6 +3249,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3275,32 +3280,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129085295</v>
+        <v>129085291</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>78797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3310,10 +3315,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768282</v>
+        <v>768164</v>
       </c>
       <c r="R28" t="n">
-        <v>7289198</v>
+        <v>7289156</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3346,11 +3351,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3380,7 +3380,7 @@
         <v>129085290</v>
       </c>
       <c r="B29" t="n">
-        <v>79059</v>
+        <v>79063</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>129085281</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>129085287</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129085301</v>
+        <v>129085277</v>
       </c>
       <c r="B11" t="n">
-        <v>92826</v>
+        <v>90562</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768280</v>
+        <v>768461</v>
       </c>
       <c r="R11" t="n">
-        <v>7289244</v>
+        <v>7289280</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,32 +1718,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085277</v>
+        <v>129085301</v>
       </c>
       <c r="B12" t="n">
-        <v>90562</v>
+        <v>92826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768461</v>
+        <v>768280</v>
       </c>
       <c r="R12" t="n">
-        <v>7289280</v>
+        <v>7289244</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129085277</v>
+        <v>129085301</v>
       </c>
       <c r="B11" t="n">
-        <v>90562</v>
+        <v>92833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768461</v>
+        <v>768280</v>
       </c>
       <c r="R11" t="n">
-        <v>7289280</v>
+        <v>7289244</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,32 +1718,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085301</v>
+        <v>129085280</v>
       </c>
       <c r="B12" t="n">
-        <v>92826</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768280</v>
+        <v>768287</v>
       </c>
       <c r="R12" t="n">
-        <v>7289244</v>
+        <v>7289247</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1789,6 +1789,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129085280</v>
+        <v>129085277</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>90569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1826,21 +1831,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768287</v>
+        <v>768461</v>
       </c>
       <c r="R13" t="n">
-        <v>7289247</v>
+        <v>7289280</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1886,11 +1891,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,7 +1920,7 @@
         <v>129085278</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>129085303</v>
       </c>
       <c r="B16" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>129085286</v>
       </c>
       <c r="B17" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>129085288</v>
       </c>
       <c r="B19" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129085302</v>
       </c>
       <c r="B20" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,32 +2596,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129085299</v>
+        <v>129085296</v>
       </c>
       <c r="B21" t="n">
-        <v>92826</v>
+        <v>56906</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>768144</v>
+        <v>768294</v>
       </c>
       <c r="R21" t="n">
-        <v>7289201</v>
+        <v>7289244</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2693,32 +2693,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129085296</v>
+        <v>129085299</v>
       </c>
       <c r="B22" t="n">
-        <v>56906</v>
+        <v>92833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768294</v>
+        <v>768144</v>
       </c>
       <c r="R22" t="n">
-        <v>7289244</v>
+        <v>7289201</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2890,7 +2890,7 @@
         <v>129085298</v>
       </c>
       <c r="B24" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129085300</v>
       </c>
       <c r="B25" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129085289</v>
       </c>
       <c r="B26" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3178,32 +3178,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129085295</v>
+        <v>129085291</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>78797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768282</v>
+        <v>768164</v>
       </c>
       <c r="R27" t="n">
-        <v>7289198</v>
+        <v>7289156</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3249,11 +3249,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3280,32 +3275,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129085291</v>
+        <v>129085295</v>
       </c>
       <c r="B28" t="n">
-        <v>78797</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3315,10 +3310,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768164</v>
+        <v>768282</v>
       </c>
       <c r="R28" t="n">
-        <v>7289156</v>
+        <v>7289198</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3351,6 +3346,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3377,32 +3377,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129085290</v>
+        <v>129085281</v>
       </c>
       <c r="B29" t="n">
-        <v>79063</v>
+        <v>57725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768447</v>
+        <v>768299</v>
       </c>
       <c r="R29" t="n">
-        <v>7289274</v>
+        <v>7289244</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3448,6 +3448,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3474,32 +3479,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129085281</v>
+        <v>129085290</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>79063</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3509,10 +3514,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768299</v>
+        <v>768447</v>
       </c>
       <c r="R30" t="n">
-        <v>7289244</v>
+        <v>7289274</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3545,11 +3550,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1420,7 +1420,7 @@
         <v>129085282</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>129085292</v>
       </c>
       <c r="B10" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129085301</v>
+        <v>129085277</v>
       </c>
       <c r="B11" t="n">
-        <v>92833</v>
+        <v>90571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768280</v>
+        <v>768461</v>
       </c>
       <c r="R11" t="n">
-        <v>7289244</v>
+        <v>7289280</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,32 +1718,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085280</v>
+        <v>129085301</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768287</v>
+        <v>768280</v>
       </c>
       <c r="R12" t="n">
-        <v>7289247</v>
+        <v>7289244</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1789,11 +1789,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129085277</v>
+        <v>129085280</v>
       </c>
       <c r="B13" t="n">
-        <v>90569</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1831,21 +1826,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768461</v>
+        <v>768287</v>
       </c>
       <c r="R13" t="n">
-        <v>7289280</v>
+        <v>7289247</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1891,6 +1886,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,7 +1920,7 @@
         <v>129085278</v>
       </c>
       <c r="B14" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>129085297</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>129085303</v>
       </c>
       <c r="B16" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>129085286</v>
       </c>
       <c r="B17" t="n">
-        <v>92864</v>
+        <v>92866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         <v>129085294</v>
       </c>
       <c r="B18" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>129085288</v>
       </c>
       <c r="B19" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129085302</v>
       </c>
       <c r="B20" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129085296</v>
       </c>
       <c r="B21" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,32 +2693,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129085299</v>
+        <v>129085293</v>
       </c>
       <c r="B22" t="n">
-        <v>92833</v>
+        <v>78799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768144</v>
+        <v>768224</v>
       </c>
       <c r="R22" t="n">
-        <v>7289201</v>
+        <v>7289102</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2790,32 +2790,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129085293</v>
+        <v>129085299</v>
       </c>
       <c r="B23" t="n">
-        <v>78797</v>
+        <v>92835</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768224</v>
+        <v>768144</v>
       </c>
       <c r="R23" t="n">
-        <v>7289102</v>
+        <v>7289201</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2890,7 +2890,7 @@
         <v>129085298</v>
       </c>
       <c r="B24" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,32 +2984,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129085300</v>
+        <v>129085289</v>
       </c>
       <c r="B25" t="n">
-        <v>92833</v>
+        <v>92839</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768288</v>
+        <v>768301</v>
       </c>
       <c r="R25" t="n">
-        <v>7289204</v>
+        <v>7289317</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3081,32 +3081,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129085289</v>
+        <v>129085300</v>
       </c>
       <c r="B26" t="n">
-        <v>92837</v>
+        <v>92835</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768301</v>
+        <v>768288</v>
       </c>
       <c r="R26" t="n">
-        <v>7289317</v>
+        <v>7289204</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3181,7 +3181,7 @@
         <v>129085291</v>
       </c>
       <c r="B27" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>129085295</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>129085281</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>129085290</v>
       </c>
       <c r="B30" t="n">
-        <v>79063</v>
+        <v>79065</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>129085287</v>
       </c>
       <c r="B31" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -2693,32 +2693,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129085293</v>
+        <v>129085299</v>
       </c>
       <c r="B22" t="n">
-        <v>78799</v>
+        <v>92835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768224</v>
+        <v>768144</v>
       </c>
       <c r="R22" t="n">
-        <v>7289102</v>
+        <v>7289201</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2790,32 +2790,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129085299</v>
+        <v>129085293</v>
       </c>
       <c r="B23" t="n">
-        <v>92835</v>
+        <v>78799</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>768144</v>
+        <v>768224</v>
       </c>
       <c r="R23" t="n">
-        <v>7289201</v>
+        <v>7289102</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2984,32 +2984,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129085289</v>
+        <v>129085300</v>
       </c>
       <c r="B25" t="n">
-        <v>92839</v>
+        <v>92835</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768301</v>
+        <v>768288</v>
       </c>
       <c r="R25" t="n">
-        <v>7289317</v>
+        <v>7289204</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3081,32 +3081,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129085300</v>
+        <v>129085289</v>
       </c>
       <c r="B26" t="n">
-        <v>92835</v>
+        <v>92839</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768288</v>
+        <v>768301</v>
       </c>
       <c r="R26" t="n">
-        <v>7289204</v>
+        <v>7289317</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3178,32 +3178,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129085291</v>
+        <v>129085295</v>
       </c>
       <c r="B27" t="n">
-        <v>78799</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768164</v>
+        <v>768282</v>
       </c>
       <c r="R27" t="n">
-        <v>7289156</v>
+        <v>7289198</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3249,6 +3249,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3275,32 +3280,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129085295</v>
+        <v>129085291</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>78799</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3310,10 +3315,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768282</v>
+        <v>768164</v>
       </c>
       <c r="R28" t="n">
-        <v>7289198</v>
+        <v>7289156</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3346,11 +3351,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3377,32 +3377,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129085281</v>
+        <v>129085290</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79065</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768299</v>
+        <v>768447</v>
       </c>
       <c r="R29" t="n">
-        <v>7289244</v>
+        <v>7289274</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3448,11 +3448,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3479,32 +3474,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129085290</v>
+        <v>129085281</v>
       </c>
       <c r="B30" t="n">
-        <v>79065</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3514,10 +3509,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768447</v>
+        <v>768299</v>
       </c>
       <c r="R30" t="n">
-        <v>7289274</v>
+        <v>7289244</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3550,6 +3545,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129085278</v>
+        <v>129085297</v>
       </c>
       <c r="B14" t="n">
-        <v>90571</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768498</v>
+        <v>768241</v>
       </c>
       <c r="R14" t="n">
-        <v>7289313</v>
+        <v>7289178</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129085297</v>
+        <v>129085278</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>90571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768241</v>
+        <v>768498</v>
       </c>
       <c r="R15" t="n">
-        <v>7289178</v>
+        <v>7289313</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1621,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129085277</v>
+        <v>129085280</v>
       </c>
       <c r="B11" t="n">
-        <v>90571</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,21 +1632,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768461</v>
+        <v>768287</v>
       </c>
       <c r="R11" t="n">
-        <v>7289280</v>
+        <v>7289247</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1692,6 +1692,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,32 +1723,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085301</v>
+        <v>129085277</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>90572</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768280</v>
+        <v>768461</v>
       </c>
       <c r="R12" t="n">
-        <v>7289244</v>
+        <v>7289280</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1815,32 +1820,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129085280</v>
+        <v>129085301</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>92821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768287</v>
+        <v>768280</v>
       </c>
       <c r="R13" t="n">
-        <v>7289247</v>
+        <v>7289244</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1886,11 +1891,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129085297</v>
+        <v>129085278</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>90572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,21 +1928,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768241</v>
+        <v>768498</v>
       </c>
       <c r="R14" t="n">
-        <v>7289178</v>
+        <v>7289313</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129085278</v>
+        <v>129085297</v>
       </c>
       <c r="B15" t="n">
-        <v>90571</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768498</v>
+        <v>768241</v>
       </c>
       <c r="R15" t="n">
-        <v>7289313</v>
+        <v>7289178</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2114,7 +2114,7 @@
         <v>129085303</v>
       </c>
       <c r="B16" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>129085286</v>
       </c>
       <c r="B17" t="n">
-        <v>92866</v>
+        <v>92852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>129085288</v>
       </c>
       <c r="B19" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129085302</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,32 +2596,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129085296</v>
+        <v>129085299</v>
       </c>
       <c r="B21" t="n">
-        <v>56908</v>
+        <v>92821</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>768294</v>
+        <v>768144</v>
       </c>
       <c r="R21" t="n">
-        <v>7289244</v>
+        <v>7289201</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2693,32 +2693,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129085299</v>
+        <v>129085296</v>
       </c>
       <c r="B22" t="n">
-        <v>92835</v>
+        <v>56908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768144</v>
+        <v>768294</v>
       </c>
       <c r="R22" t="n">
-        <v>7289201</v>
+        <v>7289244</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2890,7 +2890,7 @@
         <v>129085298</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129085300</v>
       </c>
       <c r="B25" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129085289</v>
       </c>
       <c r="B26" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>129085295</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,32 +3377,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129085290</v>
+        <v>129085281</v>
       </c>
       <c r="B29" t="n">
-        <v>79065</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768447</v>
+        <v>768299</v>
       </c>
       <c r="R29" t="n">
-        <v>7289274</v>
+        <v>7289244</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3448,6 +3448,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3474,32 +3479,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129085281</v>
+        <v>129085290</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>79065</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3509,10 +3514,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768299</v>
+        <v>768447</v>
       </c>
       <c r="R30" t="n">
-        <v>7289244</v>
+        <v>7289274</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3545,11 +3550,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129085280</v>
+        <v>129085301</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768287</v>
+        <v>768280</v>
       </c>
       <c r="R11" t="n">
-        <v>7289247</v>
+        <v>7289244</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1692,11 +1692,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085277</v>
+        <v>129085280</v>
       </c>
       <c r="B12" t="n">
-        <v>90572</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1734,21 +1729,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1758,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768461</v>
+        <v>768287</v>
       </c>
       <c r="R12" t="n">
-        <v>7289280</v>
+        <v>7289247</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1794,6 +1789,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,32 +1820,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129085301</v>
+        <v>129085277</v>
       </c>
       <c r="B13" t="n">
-        <v>92821</v>
+        <v>90572</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768280</v>
+        <v>768461</v>
       </c>
       <c r="R13" t="n">
-        <v>7289244</v>
+        <v>7289280</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2111,32 +2111,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129085303</v>
+        <v>129085286</v>
       </c>
       <c r="B16" t="n">
-        <v>92821</v>
+        <v>92853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768495</v>
+        <v>768470</v>
       </c>
       <c r="R16" t="n">
-        <v>7289476</v>
+        <v>7289279</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2208,32 +2208,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129085286</v>
+        <v>129085303</v>
       </c>
       <c r="B17" t="n">
-        <v>92852</v>
+        <v>92822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768470</v>
+        <v>768495</v>
       </c>
       <c r="R17" t="n">
-        <v>7289279</v>
+        <v>7289476</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,7 +2405,7 @@
         <v>129085288</v>
       </c>
       <c r="B19" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129085302</v>
       </c>
       <c r="B20" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129085299</v>
       </c>
       <c r="B21" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129085298</v>
       </c>
       <c r="B24" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129085300</v>
       </c>
       <c r="B25" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129085289</v>
       </c>
       <c r="B26" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>129085295</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,32 +3377,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129085281</v>
+        <v>129085290</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79065</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768299</v>
+        <v>768447</v>
       </c>
       <c r="R29" t="n">
-        <v>7289244</v>
+        <v>7289274</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3448,11 +3448,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3479,32 +3474,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129085290</v>
+        <v>129085281</v>
       </c>
       <c r="B30" t="n">
-        <v>79065</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3514,10 +3509,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768447</v>
+        <v>768299</v>
       </c>
       <c r="R30" t="n">
-        <v>7289274</v>
+        <v>7289244</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3550,6 +3545,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1621,32 +1621,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129085301</v>
+        <v>129085277</v>
       </c>
       <c r="B11" t="n">
-        <v>92822</v>
+        <v>90572</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768280</v>
+        <v>768461</v>
       </c>
       <c r="R11" t="n">
-        <v>7289244</v>
+        <v>7289280</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,32 +1718,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085280</v>
+        <v>129085301</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768287</v>
+        <v>768280</v>
       </c>
       <c r="R12" t="n">
-        <v>7289247</v>
+        <v>7289244</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1789,11 +1789,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129085277</v>
+        <v>129085280</v>
       </c>
       <c r="B13" t="n">
-        <v>90572</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1831,21 +1826,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1855,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768461</v>
+        <v>768287</v>
       </c>
       <c r="R13" t="n">
-        <v>7289280</v>
+        <v>7289247</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1891,6 +1886,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3181,7 +3181,7 @@
         <v>129085295</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3377,32 +3377,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129085290</v>
+        <v>129085281</v>
       </c>
       <c r="B29" t="n">
-        <v>79065</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768447</v>
+        <v>768299</v>
       </c>
       <c r="R29" t="n">
-        <v>7289274</v>
+        <v>7289244</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3448,6 +3448,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3474,32 +3479,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129085281</v>
+        <v>129085290</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>79065</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3509,10 +3514,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768299</v>
+        <v>768447</v>
       </c>
       <c r="R30" t="n">
-        <v>7289244</v>
+        <v>7289274</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3545,11 +3550,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>129085292</v>
       </c>
       <c r="B10" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>129085277</v>
       </c>
       <c r="B11" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129085301</v>
       </c>
       <c r="B12" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>129085278</v>
       </c>
       <c r="B14" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>129085297</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,32 +2111,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129085286</v>
+        <v>129085303</v>
       </c>
       <c r="B16" t="n">
-        <v>92853</v>
+        <v>92825</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768470</v>
+        <v>768495</v>
       </c>
       <c r="R16" t="n">
-        <v>7289279</v>
+        <v>7289476</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2208,32 +2208,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129085303</v>
+        <v>129085286</v>
       </c>
       <c r="B17" t="n">
-        <v>92822</v>
+        <v>92856</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768495</v>
+        <v>768470</v>
       </c>
       <c r="R17" t="n">
-        <v>7289476</v>
+        <v>7289279</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2405,7 +2405,7 @@
         <v>129085288</v>
       </c>
       <c r="B19" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129085302</v>
       </c>
       <c r="B20" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129085299</v>
       </c>
       <c r="B21" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>129085293</v>
       </c>
       <c r="B23" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129085298</v>
       </c>
       <c r="B24" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>129085300</v>
       </c>
       <c r="B25" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129085289</v>
       </c>
       <c r="B26" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>129085295</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>129085291</v>
       </c>
       <c r="B28" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3377,32 +3377,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129085281</v>
+        <v>129085290</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79067</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768299</v>
+        <v>768447</v>
       </c>
       <c r="R29" t="n">
-        <v>7289244</v>
+        <v>7289274</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3448,11 +3448,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3479,32 +3474,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129085290</v>
+        <v>129085281</v>
       </c>
       <c r="B30" t="n">
-        <v>79065</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3514,10 +3509,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768447</v>
+        <v>768299</v>
       </c>
       <c r="R30" t="n">
-        <v>7289274</v>
+        <v>7289244</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3550,6 +3545,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379793</v>
+        <v>129085277</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Stenglott, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768062</v>
+        <v>768461</v>
       </c>
       <c r="R2" t="n">
-        <v>7289273</v>
+        <v>7289280</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,61 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379794</v>
+        <v>129085278</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Stenglott, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768046</v>
+        <v>768498</v>
       </c>
       <c r="R3" t="n">
-        <v>7289237</v>
+        <v>7289313</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -890,11 +872,11 @@
         <v>127414918</v>
       </c>
       <c r="B4" t="n">
-        <v>92642</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -993,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127414917</v>
+        <v>129085298</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,41 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Stenglott, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768145</v>
+        <v>768330</v>
       </c>
       <c r="R5" t="n">
-        <v>7289172</v>
+        <v>7289340</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,17 +1040,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127414919</v>
+        <v>129085299</v>
       </c>
       <c r="B6" t="n">
-        <v>78787</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,41 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Stenglott, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768499</v>
+        <v>768144</v>
       </c>
       <c r="R6" t="n">
-        <v>7289354</v>
+        <v>7289201</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,17 +1137,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,64 +1157,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127414915</v>
+        <v>129085300</v>
       </c>
       <c r="B7" t="n">
-        <v>80161</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Stenglott, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768044</v>
+        <v>768288</v>
       </c>
       <c r="R7" t="n">
-        <v>7289242</v>
+        <v>7289204</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1274,17 +1234,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,64 +1254,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127414916</v>
+        <v>129085301</v>
       </c>
       <c r="B8" t="n">
-        <v>98387</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Arvidsträsk, Nb</t>
+          <t>Stenglott, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768037</v>
+        <v>768280</v>
       </c>
       <c r="R8" t="n">
-        <v>7289233</v>
+        <v>7289244</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,17 +1331,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,22 +1351,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129085282</v>
+        <v>129085302</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1452,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768301</v>
+        <v>768502</v>
       </c>
       <c r="R9" t="n">
-        <v>7289236</v>
+        <v>7289295</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1488,11 +1434,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack i flera lager, gamla och nya.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129085292</v>
+        <v>129085303</v>
       </c>
       <c r="B10" t="n">
-        <v>78802</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768190</v>
+        <v>768495</v>
       </c>
       <c r="R10" t="n">
-        <v>7289136</v>
+        <v>7289476</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1590,11 +1531,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,32 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129085301</v>
+        <v>129085288</v>
       </c>
       <c r="B11" t="n">
-        <v>92835</v>
+        <v>93201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768280</v>
+        <v>768227</v>
       </c>
       <c r="R11" t="n">
-        <v>7289244</v>
+        <v>7289279</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129085277</v>
+        <v>129085289</v>
       </c>
       <c r="B12" t="n">
-        <v>90585</v>
+        <v>93201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>768461</v>
+        <v>768301</v>
       </c>
       <c r="R12" t="n">
-        <v>7289280</v>
+        <v>7289317</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1815,48 +1751,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129085280</v>
+        <v>127414917</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenglott, Nb</t>
+          <t>Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768287</v>
+        <v>768145</v>
       </c>
       <c r="R13" t="n">
-        <v>7289247</v>
+        <v>7289172</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1880,17 +1820,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1905,44 +1845,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129085278</v>
+        <v>129085297</v>
       </c>
       <c r="B14" t="n">
-        <v>90585</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1892,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>768498</v>
+        <v>768241</v>
       </c>
       <c r="R14" t="n">
-        <v>7289313</v>
+        <v>7289178</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2014,32 +1954,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129085297</v>
+        <v>129085290</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,10 +1989,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>768241</v>
+        <v>768447</v>
       </c>
       <c r="R15" t="n">
-        <v>7289178</v>
+        <v>7289274</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2111,48 +2051,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129085286</v>
+        <v>127414919</v>
       </c>
       <c r="B16" t="n">
-        <v>92866</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenglott, Nb</t>
+          <t>Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>768470</v>
+        <v>768499</v>
       </c>
       <c r="R16" t="n">
-        <v>7289279</v>
+        <v>7289354</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2176,12 +2120,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2196,22 +2145,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129085303</v>
+        <v>126379794</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2219,34 +2168,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenglott, Nb</t>
+          <t>Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>768495</v>
+        <v>768046</v>
       </c>
       <c r="R17" t="n">
-        <v>7289476</v>
+        <v>7289237</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2273,12 +2226,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2293,22 +2251,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129085294</v>
+        <v>127414915</v>
       </c>
       <c r="B18" t="n">
-        <v>58097</v>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2316,37 +2274,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenglott, Nb</t>
+          <t>Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>768294</v>
+        <v>768044</v>
       </c>
       <c r="R18" t="n">
-        <v>7289244</v>
+        <v>7289242</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2370,12 +2332,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2390,44 +2357,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129085288</v>
+        <v>129085287</v>
       </c>
       <c r="B19" t="n">
-        <v>92839</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2437,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>768227</v>
+        <v>768220</v>
       </c>
       <c r="R19" t="n">
-        <v>7289279</v>
+        <v>7289100</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2499,32 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129085302</v>
+        <v>129085280</v>
       </c>
       <c r="B20" t="n">
-        <v>92835</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2534,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>768502</v>
+        <v>768287</v>
       </c>
       <c r="R20" t="n">
-        <v>7289295</v>
+        <v>7289247</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2570,6 +2537,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2596,10 +2568,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129085293</v>
+        <v>129085281</v>
       </c>
       <c r="B21" t="n">
-        <v>78802</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2607,21 +2579,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2631,10 +2603,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>768224</v>
+        <v>768299</v>
       </c>
       <c r="R21" t="n">
-        <v>7289102</v>
+        <v>7289244</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2667,6 +2639,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2693,32 +2670,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129085299</v>
+        <v>129085282</v>
       </c>
       <c r="B22" t="n">
-        <v>92835</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2728,10 +2705,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>768144</v>
+        <v>768301</v>
       </c>
       <c r="R22" t="n">
-        <v>7289201</v>
+        <v>7289236</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2764,6 +2741,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack i flera lager, gamla och nya.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2793,11 +2775,11 @@
         <v>129085296</v>
       </c>
       <c r="B23" t="n">
-        <v>56908</v>
+        <v>57132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2887,10 +2869,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129085298</v>
+        <v>129085294</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2898,21 +2880,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2922,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>768330</v>
+        <v>768294</v>
       </c>
       <c r="R24" t="n">
-        <v>7289340</v>
+        <v>7289244</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2984,10 +2966,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129085300</v>
+        <v>126379793</v>
       </c>
       <c r="B25" t="n">
-        <v>92835</v>
+        <v>99035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2995,34 +2977,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stenglott, Nb</t>
+          <t>Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>768288</v>
+        <v>768062</v>
       </c>
       <c r="R25" t="n">
-        <v>7289204</v>
+        <v>7289273</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3049,12 +3035,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3069,60 +3060,64 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129085289</v>
+        <v>127414916</v>
       </c>
       <c r="B26" t="n">
-        <v>92839</v>
+        <v>99035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4365</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stenglott, Nb</t>
+          <t>Arvidsträsk, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>768301</v>
+        <v>768037</v>
       </c>
       <c r="R26" t="n">
-        <v>7289317</v>
+        <v>7289233</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3146,12 +3141,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3166,44 +3166,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129085291</v>
+        <v>129085295</v>
       </c>
       <c r="B27" t="n">
-        <v>78802</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>768164</v>
+        <v>768282</v>
       </c>
       <c r="R27" t="n">
-        <v>7289156</v>
+        <v>7289198</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3249,6 +3249,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3275,32 +3280,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129085295</v>
+        <v>129085291</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3310,10 +3315,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>768282</v>
+        <v>768164</v>
       </c>
       <c r="R28" t="n">
-        <v>7289198</v>
+        <v>7289156</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3346,11 +3351,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129085281</v>
+        <v>129085292</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3388,21 +3388,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>768299</v>
+        <v>768190</v>
       </c>
       <c r="R29" t="n">
-        <v>7289244</v>
+        <v>7289136</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gamla hack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3479,32 +3479,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129085290</v>
+        <v>129085293</v>
       </c>
       <c r="B30" t="n">
-        <v>79068</v>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>768447</v>
+        <v>768224</v>
       </c>
       <c r="R30" t="n">
-        <v>7289274</v>
+        <v>7289102</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3576,32 +3576,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129085287</v>
+        <v>129085286</v>
       </c>
       <c r="B31" t="n">
-        <v>57724</v>
+        <v>93228</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>232140</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>768220</v>
+        <v>768470</v>
       </c>
       <c r="R31" t="n">
-        <v>7289100</v>
+        <v>7289279</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3670,6 +3670,205 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129085284</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stenglott, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>768232</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7289149</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129085285</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stenglott, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>768449</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7289279</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Långa hängen 40-50cm</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45432-2025 artfynd.xlsx
+++ b/artfynd/A 45432-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085277</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085278</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414918</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085298</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085299</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085300</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085301</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085302</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085303</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,6 +1701,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085288</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1748,6 +1803,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085289</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414917</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085297</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2048,6 +2118,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085290</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2154,6 +2229,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414919</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379794</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414915</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085287</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2565,6 +2660,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085280</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2667,6 +2767,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085281</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085282</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2866,6 +2976,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085296</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085294</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3069,6 +3189,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379793</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3175,6 +3300,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414916</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3277,6 +3407,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085295</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3374,6 +3509,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085291</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3476,6 +3616,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085292</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3573,6 +3718,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085293</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3670,6 +3820,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085286</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3767,6 +3922,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085284</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3869,8 +4029,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129085285</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>